--- a/library/projects/qa-sample-app/recordings/e0d149a6-6fd3-4f26-92a6-f468107f57f1/resources/testcomplete.xlsx
+++ b/library/projects/qa-sample-app/recordings/e0d149a6-6fd3-4f26-92a6-f468107f57f1/resources/testcomplete.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,29 @@
           <t>Screenshot</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Open https://www.hm.com/</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.hm.com/</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
